--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54866994</v>
+        <v>54866993</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473540.4947711756</v>
+        <v>473593</v>
       </c>
       <c r="R2" t="n">
-        <v>6997780.640366221</v>
+        <v>6997876</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,24 +757,14 @@
           <t>2015-08-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-17</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>13 skott inom 1 m2 i fuktig skog</t>
+          <t>14 skott inom 1 m2 i fuktig skog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,50 +796,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54934487</v>
+        <v>54866994</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gärde, Djupmyren / S /, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473540.4947711756</v>
+        <v>473540</v>
       </c>
       <c r="R3" t="n">
-        <v>6997780.640366221</v>
+        <v>6997781</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,24 +878,14 @@
           <t>2015-08-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-17</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I fuktig skog</t>
+          <t>13 skott inom 1 m2 i fuktig skog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,6 +914,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>54934487</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gärde, Djupmyren / S /, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>473540</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6997781</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2015-08-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I fuktig skog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>fuktig skog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39968-2024 artfynd.xlsx
+++ b/artfynd/A 39968-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54866993</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54866994</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,8 +1036,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54934487</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>